--- a/data/seed/portfolio/L-2024-8727/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-8727/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,42 +535,42 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>3911000</v>
+        <v>2752000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>273404056</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000279601273001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shartnoma №140/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №26/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>33411000</v>
+        <v>32252000</v>
       </c>
     </row>
     <row r="9">
@@ -582,35 +582,35 @@
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>2851000</v>
+        <v>2102000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Gulshan Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>393578388</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000203063907001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2075 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Mahsulot uchun to'lov, shartn. №146/26, QQS 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36262000</v>
+        <v>34354000</v>
       </c>
     </row>
     <row r="10">
@@ -620,37 +620,37 @@
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>6383000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>1553000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yulduz Meva-Sabzavot XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>210730943</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000944166144001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №1198</t>
+          <t>Оплата за продукцию по договору №31/26, НДС 12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29879000</v>
+        <v>35907000</v>
       </c>
     </row>
     <row r="11">
@@ -661,497 +661,497 @@
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>11577000</v>
+        <v>1581000</v>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Chust Polimer AJ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>307382458</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000826980511001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №7944</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №101/26</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18302000</v>
+        <v>34326000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1665000</v>
+        <v>2360000</v>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oydin Qurilish MChJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>210455483</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000313133908001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по дог. №91/20</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №161/26</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16637000</v>
+        <v>31966000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>108067000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>11577000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>216798424</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5638 за поставленный товар</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>124704000</v>
+        <v>20389000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>20416000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>1457000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №197/26 от 10.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3387</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>104288000</v>
+        <v>21846000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>3205000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>1665000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Jizzax Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>307844706</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000285165655001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2414 за поставленный товар</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>107493000</v>
+        <v>20181000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>2373000</v>
+        <v>19423000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3714 за поставленный товар</t>
+          <t>Предоплата за товар по договору №253/26 от 09.07.2026</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>109866000</v>
+        <v>39604000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>21623000</v>
+        <v>3024000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9231 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4414 09.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>131489000</v>
+        <v>42628000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1579000</v>
+        <v>4636000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farovon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>269456792</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000329032874001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Tovarlar uchun to'lov h/f №5137</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>129910000</v>
+        <v>37992000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>1579000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>3455000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9303</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>128331000</v>
+        <v>41447000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>3099000</v>
+        <v>3117000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №268/26, НДС 12%</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №5152 10.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>131430000</v>
+        <v>44564000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>6714000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>1147000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №594</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4862 10.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>124716000</v>
+        <v>45711000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>33776000</v>
+        <v>10165000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Durdona Polimer MChJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>220414702</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000598785857001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7265 за поставленный товар</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №4467</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>158492000</v>
+        <v>55876000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>5853000</v>
+        <v>8233000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Nukus Mebel MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>309525003</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000695835262001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,37 +1161,37 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shartnoma №112/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9011 13.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>164345000</v>
+        <v>64109000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>9381000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>3136000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Denov Qog'oz AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>311733422</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000418069247001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1201,117 +1201,117 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за маериалы по договору №230/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №244/26, QQS 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>154964000</v>
+        <v>67245000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>6551000</v>
+        <v>1663000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Kamalak Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>241470225</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000878585716001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1326 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8909 13.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>161515000</v>
+        <v>68908000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>2658000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>1447000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Termiz Non XK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>240405622</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000960127332001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>Shartnoma №251/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>158857000</v>
+        <v>70355000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>18181000</v>
+        <v>4259000</v>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Denov Qog'oz AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>311733422</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000418069247001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1321,907 +1321,917 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №3665</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №9895</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>140676000</v>
+        <v>66096000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46228</v>
+        <v>46216</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>11100000</v>
+        <v>19321000</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8727)</t>
+          <t>Urganch Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16307000308857468417</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8727 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за сырье по договору №200/26 от 13.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>129576000</v>
+        <v>46775000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46230</v>
+        <v>46217</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>7351000</v>
+        <v>3979000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Предопата за товар по договору №240/26 от 27.07.2026</t>
+          <t>Shartnoma №12/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>136927000</v>
+        <v>50754000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>6672000</v>
+        <v>2392000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №178/26 от 27.07.2026</t>
+          <t>SHARTNOMA №39/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>143599000</v>
+        <v>53146000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>6146000</v>
+        <v>1407000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish XK</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>273404056</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000279601273001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5127 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товар по с/ф №1129 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>149745000</v>
+        <v>54553000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>1040000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>1329000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Nukus Mebel MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>309525003</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000528007214001</t>
+          <t>20208000695835262001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товар по счет-фактуре №5861 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>148705000</v>
+        <v>55882000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46231</v>
+        <v>46218</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>5088000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>1579000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Denov Avto Ehtiyot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>385935783</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000842030639001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1402 от 28.07.2026, в т.ч. НДС 12%</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>153793000</v>
+        <v>54303000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46231</v>
+        <v>46218</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4908000</v>
+        <v>1579000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1763</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>148885000</v>
+        <v>52724000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46232</v>
+        <v>46218</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>2121000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>2690000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8410 за поставленный товар</t>
+          <t>Оплата за товары согласно с/ф №690</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>151006000</v>
+        <v>50034000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46232</v>
+        <v>46219</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>13798000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>1152000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gulshan Trans Servis XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>340834180</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000246195897001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5645</t>
+          <t>Shartnoma №136/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>137208000</v>
+        <v>51186000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46234</v>
+        <v>46219</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>2828000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>3881000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Kattaqo'rg'on Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>345900559</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000282828529001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8755 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №97/26</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>140036000</v>
+        <v>47305000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>13505000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Nukus Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>309525003</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000695835262001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>Tovar uchun to'lov, hisob-faktra №65 17.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>139736000</v>
+        <v>60810000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>112716000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>6518000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №272/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №283/26, QQS 12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>27020000</v>
+        <v>67328000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46237</v>
+        <v>46220</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>3545000</v>
+        <v>1068000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1455 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №46/26, QQS 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>30565000</v>
+        <v>68396000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46237</v>
+        <v>46220</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>1978000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>5335000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>273342244</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000806924702001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №100/26 от 03.08.2026</t>
+          <t>Transport xizmatlari uchunto'lov, shartn. №38/26</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>32543000</v>
+        <v>63061000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>1463000</v>
+        <v>5904000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Shartnoma №110/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №29/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>34006000</v>
+        <v>68965000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>1059000</v>
+        <v>3079000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Denov Avto Ehtiyot MChJ</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>385935783</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000842030639001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договор №84/26, НДС 12%</t>
+          <t>Yetkazilgan tovr uchun to'lov h/f №480</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>35065000</v>
+        <v>72044000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>959000</v>
+        <v>1838000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Denov Avto Ehtiyot MChJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>385935783</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000842030639001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №426 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №261/26, QQS 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>36024000</v>
+        <v>73882000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>949000</v>
+        <v>997000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Namangan Tur Servis XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>344286442</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000563018988001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №70/26, НДС 12%</t>
+          <t>Shartnoma №261/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>36973000</v>
+        <v>74879000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>829000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>4641000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>370959502</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000273949188001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №500 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №154/26</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>37802000</v>
+        <v>70238000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46237</v>
+        <v>46224</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>3066000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>18173000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gulshan Trans Servis XK</t>
+          <t>Namangan Tur Servis XK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>340834180</t>
+          <t>344286442</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000246195897001</t>
+          <t>20208000563018988001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №206/26 от 03.08.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №3274 21.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>34736000</v>
+        <v>88411000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46237</v>
+        <v>46224</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>6318000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>1146000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gulshan Ip-Kalava MChJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>340694567</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000283290328001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4086</t>
+          <t>Shartnoma №19/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28418000</v>
+        <v>89557000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46238</v>
+        <v>46224</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>3281000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>2740000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1678 за поставленный товар</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>31699000</v>
+        <v>86817000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>820000</v>
+        <v>3323000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2231,77 +2241,77 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №118/26, НДС 12%</t>
+          <t>SHARTNOMA №112/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>32519000</v>
+        <v>90140000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>708000</v>
+        <v>988000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Samarqand Polimer MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>266258928</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000964209710001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7750 от 04.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №84/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>33227000</v>
+        <v>91128000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>51113000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>5976000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2311,112 +2321,112 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №227/26 ОТ 04.08.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №67/26, QQS 12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>-17886000</v>
+        <v>97104000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46239</v>
+        <v>46226</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>11822000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>1040000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000570107309001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф 8592 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>-6064000</v>
+        <v>96064000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46239</v>
+        <v>46226</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>4222000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>57640000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4735 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №280/26</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>-1842000</v>
+        <v>38424000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46239</v>
+        <v>46228</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>9865000</v>
+        <v>11100000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8727)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>16307000308857468417</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2426,237 +2436,237 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Kredit shartnomasi L-2024-8727 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>-11707000</v>
+        <v>27324000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46240</v>
+        <v>46230</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>1086000</v>
+        <v>6856000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish XK</t>
+          <t>Kamalak Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>273404056</t>
+          <t>241470225</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000279601273001</t>
+          <t>20208000878585716001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №85/26, НДС 12%</t>
+          <t>Shartnoma №174/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>-10621000</v>
+        <v>34180000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46241</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>6533000</v>
+        <v>1406000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7456 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6658</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>-4088000</v>
+        <v>35586000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46241</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>1858000</v>
+        <v>1171000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2349 за поставленный товар</t>
+          <t>Shartnoma №280/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>-2230000</v>
+        <v>36757000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46241</v>
+        <v>46230</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>1010000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>2336000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9785 07.08.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun t'lov, shartn. №244/26</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>-1220000</v>
+        <v>34421000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46241</v>
+        <v>46230</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>993000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>6925000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1569 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №78/26</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>-227000</v>
+        <v>27496000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>52662000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>24229000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Denov Avto Ehtiyot MChJ</t>
+          <t>Farovon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>385935783</t>
+          <t>269456792</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000842030639001</t>
+          <t>20208000329032874001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2666,37 +2676,37 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №214/26 от 10.08.2026</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №217/26</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>52435000</v>
+        <v>3267000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46244</v>
+        <v>46231</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>21415000</v>
+        <v>2466000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Andijon Sut Mahsulotlari MChJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>279442864</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000265630189001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2706,197 +2716,197 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №84/26 от 10.08.2026</t>
+          <t>Предоплата за товар по договору №128/26 от 28.07.2026</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>73850000</v>
+        <v>5733000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46244</v>
+        <v>46231</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>690000</v>
+        <v>1340000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3880 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №29/26, НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>74540000</v>
+        <v>7073000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46244</v>
+        <v>46231</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>1419000</v>
+        <v>3169000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oydin Qurilish MChJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>210455483</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000313133908001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartn. №91/20</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №206/26</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>73121000</v>
+        <v>3904000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46244</v>
+        <v>46231</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>3162000</v>
+        <v>30801000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>273342244</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000806924702001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1278</t>
+          <t>Оплата за транспортные услуги по договору №42/26</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>69959000</v>
+        <v>-26897000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46245</v>
+        <v>46232</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>1180000</v>
+        <v>3214000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>273404056</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000279601273001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5092 за поставленный товар</t>
+          <t>Shartnoma №204/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>71139000</v>
+        <v>-23683000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46245</v>
+        <v>46232</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>1842000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>2889000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2906,77 +2916,77 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6993</t>
+          <t>Shartnoma №171/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>69297000</v>
+        <v>-20794000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46245</v>
+        <v>46232</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>4288000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>1506000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gulshan Trans Servis XK</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>340834180</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000246195897001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №243/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4370</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>65009000</v>
+        <v>-19288000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46246</v>
+        <v>46232</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>9523000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>1842000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Durdona Polimer MChJ</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>220414702</t>
+          <t>273342244</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000598785857001</t>
+          <t>20208000806924702001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2986,437 +2996,432 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №122/26 от 12.08.2026</t>
+          <t>Tovarlar uchun to'lov h/f №3124</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>74532000</v>
+        <v>-21130000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46247</v>
+        <v>46232</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>5317000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>3840000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Denov Avto Ehtiyot MChJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>385935783</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000842030639001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4317 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №115/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>79849000</v>
+        <v>-24970000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46247</v>
+        <v>46233</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>1486000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>1115000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gulshan Ip-Kalava MChJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>340694567</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000283290328001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9211</t>
+          <t>Mahsulot uchun to'lov, shartnoma №3/26, QQS 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>78363000</v>
+        <v>-23855000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46248</v>
+        <v>46233</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>868000</v>
+        <v>998000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №926 14.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №190/26, QQS 12%</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>79231000</v>
+        <v>-22857000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46251</v>
+        <v>46233</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>2223000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>14690000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Tong Moy XK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>333457061</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000660958864001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №279/26 от 17.08.2026</t>
+          <t>Tovarlar uchun to'lov h/f №3195</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>81454000</v>
+        <v>-37547000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>857000</v>
+        <v>50827000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №282/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5887</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>82311000</v>
+        <v>13280000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>1345000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>15878000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bunyodkor Polimer AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>215627731</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000809589460001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №1978 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>80966000</v>
+        <v>29158000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>1345000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>3255000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>353835693</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000600013397001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №276/26, QQS 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>79621000</v>
+        <v>32413000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>5344000</v>
+        <v>300000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>248095250</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3737</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>74277000</v>
+        <v>32113000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>13107000</v>
+        <v>3112000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>273342244</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000806924702001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №72/26 от 17.08.2026, НДС 12%</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №5635</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>61170000</v>
+        <v>29001000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>4894000</v>
+        <v>59434000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2157 от 19.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6691 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>66064000</v>
+        <v>88435000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>1292000</v>
+        <v>29174000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Kamalak Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>241470225</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000878585716001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3426,397 +3431,392 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №268/26 от 19.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №441 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>67356000</v>
+        <v>117609000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>1138000</v>
+        <v>6263000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Samarqand Polimer MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>266258928</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000964209710001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8691 19.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №211/26, НДС 12%</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>68494000</v>
+        <v>123872000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46253</v>
+        <v>46237</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>1011000</v>
+        <v>2573000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Shartnoma №20/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №53/26, НДС 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>69505000</v>
+        <v>126445000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46254</v>
+        <v>46237</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>990000</v>
+        <v>2222000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6869 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №264/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>70495000</v>
+        <v>128667000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46255</v>
+        <v>46237</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>1126000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>2587000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5138 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №30/26, QQS bilan</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>71621000</v>
+        <v>126080000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46258</v>
+        <v>46237</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>11111000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>6154000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №186/26 от 24.08.2026</t>
+          <t>Tovarlar uchun to'lov h/f №1437</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>82732000</v>
+        <v>119926000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46258</v>
+        <v>46237</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>8895000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>14717000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Tong Moy XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>333457061</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000660958864001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №132/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ТОАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №9866</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>91627000</v>
+        <v>105209000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46258</v>
+        <v>46238</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>2085000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>9865000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>351558349</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №221/26 от 24.08.2026</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>93712000</v>
+        <v>95344000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>1925000</v>
+        <v>1580000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Shatnoma №267/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1338</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>95637000</v>
+        <v>96924000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>1354000</v>
+        <v>8690000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Termiz Non XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>240405622</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000960127332001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9315 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №248/26, QQS 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>96991000</v>
+        <v>105614000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>887000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>5738000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Termiz Non XK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>240405622</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000528007214001</t>
+          <t>20208000960127332001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3826,432 +3826,437 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Mahsulot uchun to'lov, shartnoma №239/26, QQS 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>96104000</v>
+        <v>111352000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>2380000</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n">
+        <v>3909000</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Namangan Tur Servis XK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>344286442</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000563018988001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Mahsulot uchun to'lov, shartnoma №164/26, QQS 12%</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>93724000</v>
+        <v>115261000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>2401000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>1162000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gulshan Trans Servis XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>340834180</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000246195897001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7471</t>
+          <t>Tovar uchun to'lov, h/f №4096 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>91323000</v>
+        <v>116423000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>3528000</v>
+        <v>1419000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Denov Qog'oz AJ</t>
+          <t>Jizzax Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>311733422</t>
+          <t>307844706</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000418069247001</t>
+          <t>20208000285165655001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №16</t>
+          <t>Арендная плата за август 2026 г. по договору №34/22</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>87795000</v>
+        <v>115004000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>15131000</v>
+        <v>6575000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №176/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №6265</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>72664000</v>
+        <v>108429000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46259</v>
+        <v>46244</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>2653000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>18659000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Guliston Poligraf MChJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>211140733</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000546065669001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №63/26, QQS 12%</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №3944</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>75317000</v>
+        <v>89770000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46259</v>
+        <v>46244</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>2341000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>29523000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №63/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №189/26</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>77658000</v>
+        <v>60247000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46259</v>
+        <v>46246</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>7015000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>4974000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №222/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6395</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>70643000</v>
+        <v>65221000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46259</v>
+        <v>46246</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>11100000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>4541000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8727)</t>
+          <t>Shahrisabz Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>16307000308857468417</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8727 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Yetkazilgan toar uchun to'lov h/f №8058</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>59543000</v>
+        <v>69762000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46260</v>
+        <v>46246</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>12185000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>18517000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7905</t>
+          <t>Tovarlar uchun to'lov h/f №4866</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>71728000</v>
+        <v>51245000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46260</v>
+        <v>46247</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>2304000</v>
+        <v>1986000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Guliston Poligraf MChJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>211140733</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000546065669001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №87/26 от 26.08.2026</t>
+          <t>Tovar uchun to'lov, h/f №1471 13.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>74032000</v>
+        <v>53231000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46260</v>
+        <v>46247</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>1756000</v>
+        <v>1485000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4261,37 +4266,37 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №71/26 от 26.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7039 13.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>75788000</v>
+        <v>54716000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46260</v>
+        <v>46247</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>1573000</v>
+        <v>1155000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Nukus Mebel MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>309525003</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000695835262001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4301,1107 +4306,1102 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5537 от 26.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4724</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>77361000</v>
+        <v>55871000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46262</v>
+        <v>46247</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>1684000</v>
+        <v>36704000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8365</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №81/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>75677000</v>
+        <v>19167000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46262</v>
+        <v>46251</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>2734000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>21824000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Gulshan Trans Servis XK</t>
+          <t>Termiz Non XK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>340834180</t>
+          <t>240405622</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000246195897001</t>
+          <t>20208000960127332001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №7385</t>
+          <t>Оплата за продукцию по дог. №1/26, НДС 12%</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>72943000</v>
+        <v>40991000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46262</v>
+        <v>46251</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>4705000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>3216000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gulshan Trans Servis XK</t>
+          <t>Termiz Non XK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>340834180</t>
+          <t>240405622</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000246195897001</t>
+          <t>20208000960127332001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №37/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5957</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>68238000</v>
+        <v>44207000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>1872000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>1345000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5491 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Ijtimoiy soliq iyul 2026</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>70110000</v>
+        <v>42862000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>300000</v>
+        <v>1345000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>КОМИССИЯ ЗА ПЕРЕВОД</t>
+          <t>Jismoniy shaxslar daromad olig'i iyul 2026</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>69810000</v>
+        <v>41517000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2197000</v>
+        <v>4639000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Buxoro Agro AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>347709595</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000272739491001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №28/26 от 31.08.2026, НДС 12%</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №217/26</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>67613000</v>
+        <v>36878000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>33564000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>3424000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chust Sut AJ</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>395073824</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000838269805001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1584</t>
+          <t>Mahsulot uchun to'lov, shartn. №166/26, QQS 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>34049000</v>
+        <v>40302000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46267</v>
+        <v>46253</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>2854000</v>
+        <v>2472000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2991 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7340 19.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>36903000</v>
+        <v>42774000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46268</v>
+        <v>46255</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>12933000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>2390000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6213 от 03.09.2026, в т.ч. НДС 12%</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>49836000</v>
+        <v>40384000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46268</v>
+        <v>46255</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>28280000</v>
+        <v>6136000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gulshan Ip-Kalava MChJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>340694567</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000283290328001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5302</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №199/26</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>21556000</v>
+        <v>34248000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46269</v>
+        <v>46258</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>5085000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>4133000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Marg'ilon Dori-Darmon MChJ</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>366334570</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000146609588001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №277/26</t>
+          <t>Предоплата за товар по договору №286/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>16471000</v>
+        <v>38381000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>806000</v>
+        <v>3926000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1420 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3304</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>17277000</v>
+        <v>42307000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>8964000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>2863000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Shahrisabz Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4669</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>8313000</v>
+        <v>45170000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46273</v>
+        <v>46258</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n">
-        <v>4620000</v>
-      </c>
+      <c r="C116" s="2" t="n">
+        <v>2706000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>273342244</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000806924702001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №273/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №230/26</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>12933000</v>
+        <v>42464000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46273</v>
+        <v>46258</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>2737000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>8078000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>273342244</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000806924702001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №88/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №233/26</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>15670000</v>
+        <v>34386000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46273</v>
+        <v>46258</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>1289000</v>
+        <v>11738000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Oydin Qurilish MChJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>210455483</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000313133908001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Арендная плата за сентябрь 2026 г. по договору №91/20</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №34/26, QQS bilan</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>14381000</v>
+        <v>22648000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46274</v>
+        <v>46259</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>2676000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish XK</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>273404056</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8727)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000279601273001</t>
+          <t>16307000308857468417</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7445 09.09.2026, QQS BILAN</t>
+          <t>Kredit shartnomasi L-2024-8727 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>17057000</v>
+        <v>11548000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>2512000</v>
+        <v>2930000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Marg'ilon Moy AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>368538356</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000316000133001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6060 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3741 26.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>19569000</v>
+        <v>14478000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46274</v>
+        <v>46261</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>1153000</v>
+        <v>5530000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Termiz Non XK</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>240405622</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000960127332001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №259/26 от 09.09.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5394</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>20722000</v>
+        <v>20008000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46275</v>
+        <v>46261</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>38952000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>887000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000570107309001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9856 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>59674000</v>
+        <v>19121000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>1985000</v>
+        <v>8496000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Andijon Sut Mahsulotlari MChJ</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>279442864</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000265630189001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Shartnoma №294/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №241/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>61659000</v>
+        <v>27617000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>1134000</v>
+        <v>5433000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Denov Avto Ehtiyot MChJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>385935783</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000842030639001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Shartnoma №193/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3915 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>62793000</v>
+        <v>33050000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46276</v>
+        <v>46265</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>3974000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Andijon Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>279442864</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000265630189001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8938 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>66767000</v>
+        <v>32750000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46279</v>
+        <v>46267</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>16333000</v>
+        <v>8653000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5561 за поставленный товар</t>
+          <t>Shartnoma №85/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>83100000</v>
+        <v>41403000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>7670000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>2635000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Denov Avto Ehtiyot MChJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>385935783</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000842030639001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9909 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №109/26</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>90770000</v>
+        <v>38768000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>2522000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>2096000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Durdona Polimer MChJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>220414702</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000598785857001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №255/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №207/26</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>93292000</v>
+        <v>36672000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>2470000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>8964000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>216798424</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №95/26, НДС 12%</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>95762000</v>
+        <v>27708000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46279</v>
+        <v>46273</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>1480000</v>
+        <v>28134000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Qo'qon Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>353835693</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000600013397001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5411,171 +5411,171 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №80/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9036 08.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>97242000</v>
+        <v>55842000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>1314000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>1289000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Jizzax Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>307844706</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000285165655001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №150/26, НДС 12%</t>
+          <t>Bino ijarasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>98556000</v>
+        <v>54553000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>835000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>3795000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>273342244</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000806924702001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору№33/26 от 14.09.2026</t>
+          <t>Оплата за сырье по договору №251/26 от 10.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>99391000</v>
+        <v>50758000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>814000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>21332000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №80/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №298/26</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>100205000</v>
+        <v>29426000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>1222000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>9914000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №211/26, QQS 12%</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>98983000</v>
+        <v>39340000</v>
       </c>
     </row>
     <row r="135">
@@ -5585,623 +5585,623 @@
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>1222000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>5109000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6769 14.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>97761000</v>
+        <v>44449000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>7456000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>1222000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5677 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>105217000</v>
+        <v>43227000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>8748000</v>
+        <v>1222000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №59/26 от 15.09.2026, НДС 12%</t>
+          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>96469000</v>
+        <v>42005000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>20496000</v>
+        <v>9057000</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Denov Qog'oz AJ</t>
+          <t>Zafar Metall Servis XK</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>311733422</t>
+          <t>265248130</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000418069247001</t>
+          <t>20208000637410355001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №137/26</t>
+          <t>Tovarlar uchun to'lov h/f №8828</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>75973000</v>
+        <v>32948000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>12537000</v>
+        <v>15697000</v>
       </c>
       <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Zafar Metall Servis XK</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>265248130</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000637410355001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №73/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №299/26</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>63436000</v>
+        <v>17251000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>2052000</v>
+        <v>3573000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №100/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №222/26, НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>65488000</v>
+        <v>20824000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>1303000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>3071000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Durdona Polimer MChJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>220414702</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000598785857001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8872</t>
+          <t>Предоплата за материалы по договору №182/26</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>66791000</v>
+        <v>17753000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>1232000</v>
+        <v>16043000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Andijon Savdo MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>214073315</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000606566971001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №108/26 от 21.09.2026</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №174/26, QQS 12%</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>68023000</v>
+        <v>33796000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>820000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>13603000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>273342244</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000806924702001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №48/26, НДС 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №22/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>68843000</v>
+        <v>20193000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>2101000</v>
+        <v>36589000</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Moy XK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>333457061</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000660958864001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
+          <t>Tovarlar uchun to'lov h/f №7719</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>66742000</v>
+        <v>-16396000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>10305000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>4051000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №371 от 22.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f 521</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>77047000</v>
+        <v>-20447000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>4381000</v>
+        <v>30129000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Termiz Non XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>240405622</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000960127332001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7044 от 23.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №120/26, НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>81428000</v>
+        <v>9682000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>2136000</v>
+        <v>10380000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7691 от 23.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4814 21.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>83564000</v>
+        <v>20062000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>2489000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>2152000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Chust Polimer AJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>307382458</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000826980511001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9258 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №199</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>86053000</v>
+        <v>17910000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>1349000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>2264000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Tong Moy XK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>333457061</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000660958864001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8590 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №2839</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>87402000</v>
+        <v>15646000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>806000</v>
+        <v>9308000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Shahrisabz Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>370959502</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000528007214001</t>
+          <t>20208000273949188001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6211,112 +6211,117 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товары согласно счет-фактуре №6749</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>86596000</v>
+        <v>6338000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>4470000</v>
+        <v>24910000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Nukus Mebel XK</t>
+          <t>Chust Polimer AJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>248095250</t>
+          <t>307382458</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000306958352001</t>
+          <t>20208000826980511001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №295/26 от 25.09.2026, НДС 12%</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №1396</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>82126000</v>
+        <v>-18572000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>11100000</v>
+        <v>2163000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8727)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>16307000308857468417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8727 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>71026000</v>
+        <v>-20735000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>4913000</v>
+        <v>3782000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6326,171 +6331,166 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5516 28.09.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6604 23.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>75939000</v>
+        <v>-16953000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>3937000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>806000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000570107309001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7020</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>79876000</v>
+        <v>-17759000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>2347000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>3387000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №63/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №89/26</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>82223000</v>
+        <v>-21146000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>1619000</v>
+        <v>7413000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Samarqand Polimer MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>266258928</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000964209710001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №38/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №100/26, QQS 12%</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>83842000</v>
+        <v>-13733000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>933000</v>
-      </c>
+      <c r="C157" s="2" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish XK</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>273404056</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8727)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000279601273001</t>
+          <t>16307000308857468417</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1781</t>
+          <t>Kredit shartnomasi L-2024-8727 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>84775000</v>
+        <v>-24833000</v>
       </c>
     </row>
     <row r="158">
@@ -6500,143 +6500,143 @@
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>8028000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>23418000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Yulduz Meva-Sabzavot XK</t>
+          <t>Termiz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>210730943</t>
+          <t>255834985</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000944166144001</t>
+          <t>20208000535063632001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7125</t>
+          <t>Mahsulot uchun to'lov, shartnoma №48/26, QQS 12%</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>76747000</v>
+        <v>-1415000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
       <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="n">
-        <v>2604000</v>
+        <v>5825000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6786</t>
+          <t>SHARTNOMA №98/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>79351000</v>
+        <v>4410000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>2373000</v>
+        <v>5240000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>351558349</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8378 за поставленный товар</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №135/26, QQS 12%</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>81724000</v>
+        <v>9650000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>6338000</v>
+        <v>4740000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Nukus Mebel MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>309525003</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000695835262001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6646,91 +6646,91 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №83/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2431 28.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>88062000</v>
+        <v>14390000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>3371000</v>
-      </c>
+      <c r="C162" s="2" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Afrosiyob Meva Eksport AJ</t>
+          <t>Urganch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>216798424</t>
+          <t>283418052</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000437369456001</t>
+          <t>20208000619589799001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №175/26 от 30.09.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №147/26, QQS bilan</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>91433000</v>
+        <v>12690000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="n">
-        <v>2597000</v>
+        <v>17910000</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Durdona Polimer MChJ</t>
+          <t>Shahrisabz Mato MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>220414702</t>
+          <t>379842404</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000598785857001</t>
+          <t>20208000736945642001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №166/26 от 30.09.2026</t>
+          <t>Shartnoma №276/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>94030000</v>
+        <v>30600000</v>
       </c>
     </row>
     <row r="164">
@@ -6740,137 +6740,57 @@
       <c r="B164" t="n">
         <v>256</v>
       </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>793000</v>
-      </c>
+      <c r="C164" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Gulshan Metall Servis XK</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>351558349</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000505350636001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7188 30.09.2026, QQS bilan</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>94823000</v>
+        <v>30300000</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B165" t="n">
-        <v>257</v>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Yangi Asr Bank</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Bank xizmati uchun komissiya</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>94523000</v>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="n">
+        <v>606965000</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>607765000</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B166" t="n">
-        <v>258</v>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>64223000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Gulshan Trans Servis XK</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>340834180</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000246195897001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по дог. №216/26 от 30.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="n">
         <v>30300000</v>
       </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="n">
-        <v>594192000</v>
-      </c>
-      <c r="D167" s="4" t="n">
-        <v>594992000</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="n">
-        <v>30300000</v>
-      </c>
-      <c r="D168" s="4" t="n"/>
+      <c r="D166" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
